--- a/cet4/result/41_校园甜宠_圣诞夜的恋爱契约/41_校园甜宠_圣诞夜的恋爱契约_学习版.xlsx
+++ b/cet4/result/41_校园甜宠_圣诞夜的恋爱契约/41_校园甜宠_圣诞夜的恋爱契约_学习版.xlsx
@@ -397,1221 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>cold</v>
       </c>
       <c r="B2" t="str">
-        <v>cold</v>
+        <v>/koʊld/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D2" t="str">
         <v>寒冷的</v>
       </c>
-      <c r="D2" t="str">
-        <v>cold(寒冷的)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>educate</v>
       </c>
       <c r="B3" t="str">
-        <v>educate</v>
+        <v>/ˈedʒukeɪt/</v>
       </c>
       <c r="C3" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D3" t="str">
         <v>教育</v>
       </c>
-      <c r="D3" t="str">
-        <v>educate(教育)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>front</v>
       </c>
       <c r="B4" t="str">
-        <v>front</v>
+        <v>/frʌnt/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D4" t="str">
         <v>前面</v>
       </c>
-      <c r="D4" t="str">
-        <v>front(前面)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>tree</v>
       </c>
       <c r="B5" t="str">
-        <v>tree</v>
+        <v>/triː/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D5" t="str">
         <v>树</v>
       </c>
-      <c r="D5" t="str">
-        <v>tree(树)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>sheet</v>
       </c>
       <c r="B6" t="str">
-        <v>sheet</v>
+        <v>/ʃiːt/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>表格</v>
       </c>
-      <c r="D6" t="str">
-        <v>sheet(表格)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>west</v>
       </c>
       <c r="B7" t="str">
-        <v>west</v>
+        <v>/west/</v>
       </c>
       <c r="C7" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D7" t="str">
         <v>西区</v>
       </c>
-      <c r="D7" t="str">
-        <v>west(西区)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>British</v>
       </c>
       <c r="B8" t="str">
-        <v>British</v>
+        <v>/ˈbrɪtɪʃ/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>英国的</v>
       </c>
-      <c r="D8" t="str">
-        <v>British(英国的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>characteristic</v>
       </c>
       <c r="B9" t="str">
-        <v>characteristic</v>
+        <v>/ˌkærəktəˈrɪstɪk/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>特征</v>
       </c>
-      <c r="D9" t="str">
-        <v>characteristic(特征)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>monthly</v>
       </c>
       <c r="B10" t="str">
-        <v>monthly</v>
+        <v>/ˈmʌnθli/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D10" t="str">
         <v>每月的</v>
       </c>
-      <c r="D10" t="str">
-        <v>monthly(每月的)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>poor</v>
       </c>
       <c r="B11" t="str">
-        <v>poor</v>
+        <v>/pʊr,pɔːr/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D11" t="str">
         <v>贫困的</v>
       </c>
-      <c r="D11" t="str">
-        <v>poor(贫困的)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>clothe</v>
       </c>
       <c r="B12" t="str">
-        <v>clothe</v>
+        <v>/kloʊð/</v>
       </c>
       <c r="C12" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D12" t="str">
         <v>给...穿衣</v>
       </c>
-      <c r="D12" t="str">
-        <v>clothe(给...穿衣)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>choice</v>
       </c>
       <c r="B13" t="str">
-        <v>choice</v>
+        <v>/tʃɔɪs/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>选择</v>
       </c>
-      <c r="D13" t="str">
-        <v>choice(选择)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>atom</v>
       </c>
       <c r="B14" t="str">
-        <v>atom</v>
+        <v>/ˈætəm/</v>
       </c>
       <c r="C14" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>原子</v>
       </c>
-      <c r="D14" t="str">
-        <v>atom(原子)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>chart</v>
       </c>
       <c r="B15" t="str">
-        <v>chart</v>
+        <v>/tʃɑːrt/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D15" t="str">
         <v>图表</v>
       </c>
-      <c r="D15" t="str">
-        <v>chart(图表)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>volt</v>
       </c>
       <c r="B16" t="str">
-        <v>volt</v>
+        <v>/voʊlt/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>伏特</v>
       </c>
-      <c r="D16" t="str">
-        <v>volt(伏特)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>afternoon</v>
       </c>
       <c r="B17" t="str">
-        <v>afternoon</v>
+        <v>/ˌæftərˈnuːn/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>下午</v>
       </c>
-      <c r="D17" t="str">
-        <v>afternoon(下午)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>excellent</v>
       </c>
       <c r="B18" t="str">
-        <v>excellent</v>
+        <v>/ˈeksələnt/</v>
       </c>
       <c r="C18" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>优秀的</v>
       </c>
-      <c r="D18" t="str">
-        <v>excellent(优秀的)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>gown</v>
       </c>
       <c r="B19" t="str">
-        <v>gown</v>
+        <v>/ɡaʊn/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D19" t="str">
         <v>长袍</v>
       </c>
-      <c r="D19" t="str">
-        <v>gown(长袍)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>extreme</v>
       </c>
       <c r="B20" t="str">
-        <v>extreme</v>
+        <v>/ɪkˈstriːm/</v>
       </c>
       <c r="C20" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>极端的</v>
       </c>
-      <c r="D20" t="str">
-        <v>extreme(极端的)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>cell</v>
       </c>
       <c r="B21" t="str">
-        <v>sheet</v>
+        <v>/sel/</v>
       </c>
       <c r="C21" t="str">
-        <v>表格</v>
+        <v>n./vi.</v>
       </c>
       <c r="D21" t="str">
-        <v>sheet(表格)📢</v>
+        <v>单元格</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>mostly</v>
       </c>
       <c r="B22" t="str">
-        <v>cell</v>
+        <v>/ˈmoʊstli/</v>
       </c>
       <c r="C22" t="str">
-        <v>单元格</v>
+        <v>v./adv.</v>
       </c>
       <c r="D22" t="str">
-        <v>cell(单元格)📢</v>
+        <v>主要</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>concern</v>
       </c>
       <c r="B23" t="str">
-        <v>mostly</v>
+        <v>/kənˈsɜːrn/</v>
       </c>
       <c r="C23" t="str">
-        <v>主要</v>
+        <v>n./vt.</v>
       </c>
       <c r="D23" t="str">
-        <v>mostly(主要)📢</v>
+        <v>关心</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>strong</v>
       </c>
       <c r="B24" t="str">
-        <v>concern</v>
+        <v>/strɔːŋ/</v>
       </c>
       <c r="C24" t="str">
-        <v>关心</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D24" t="str">
-        <v>concern(关心)📢</v>
+        <v>强壮的，强大的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>juice</v>
       </c>
       <c r="B25" t="str">
-        <v>strong</v>
+        <v>/dʒuːs/</v>
       </c>
       <c r="C25" t="str">
-        <v>强壮的，强大的</v>
+        <v>n.</v>
       </c>
       <c r="D25" t="str">
-        <v>strong(强壮的，强大的)📢</v>
+        <v>果汁</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>quarterly</v>
       </c>
       <c r="B26" t="str">
-        <v>juice</v>
+        <v>/ˈkwɔːrtərli/</v>
       </c>
       <c r="C26" t="str">
-        <v>果汁</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D26" t="str">
-        <v>juice(果汁)📢</v>
+        <v>季刊</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>Christmas</v>
       </c>
       <c r="B27" t="str">
-        <v>tree</v>
+        <v>/ˈkrɪsməs/</v>
       </c>
       <c r="C27" t="str">
-        <v>树</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>tree(树)📢</v>
+        <v>圣诞节</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>event</v>
       </c>
       <c r="B28" t="str">
-        <v>quarterly</v>
+        <v>/ɪˈvent/</v>
       </c>
       <c r="C28" t="str">
-        <v>季刊</v>
+        <v>n.</v>
       </c>
       <c r="D28" t="str">
-        <v>quarterly(季刊)📢</v>
+        <v>活动</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>store</v>
       </c>
       <c r="B29" t="str">
-        <v>afternoon</v>
+        <v>/stɔːr/</v>
       </c>
       <c r="C29" t="str">
-        <v>下午</v>
+        <v>n./vt.</v>
       </c>
       <c r="D29" t="str">
-        <v>afternoon(下午)📢</v>
+        <v>商店</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>expensive</v>
       </c>
       <c r="B30" t="str">
-        <v>Christmas</v>
+        <v>/ɪkˈspensɪv/</v>
       </c>
       <c r="C30" t="str">
-        <v>圣诞节</v>
+        <v>adj.</v>
       </c>
       <c r="D30" t="str">
-        <v>Christmas(圣诞节)📢</v>
+        <v>昂贵的</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>faithful</v>
       </c>
       <c r="B31" t="str">
-        <v>event</v>
+        <v>/ˈfeɪθfl/</v>
       </c>
       <c r="C31" t="str">
-        <v>活动</v>
+        <v>n./adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>event(活动)📢</v>
+        <v>忠实的</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>salad</v>
       </c>
       <c r="B32" t="str">
-        <v>tree</v>
+        <v>/ˈsæləd/</v>
       </c>
       <c r="C32" t="str">
-        <v>树</v>
+        <v>n.</v>
       </c>
       <c r="D32" t="str">
-        <v>tree(树)📢</v>
+        <v>沙拉</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>couple</v>
       </c>
       <c r="B33" t="str">
-        <v>store</v>
+        <v>/ˈkʌpl/</v>
       </c>
       <c r="C33" t="str">
-        <v>商店</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>store(商店)📢</v>
+        <v>一对</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>half</v>
       </c>
       <c r="B34" t="str">
-        <v>expensive</v>
+        <v>/hæf/</v>
       </c>
       <c r="C34" t="str">
-        <v>昂贵的</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D34" t="str">
-        <v>expensive(昂贵的)📢</v>
+        <v>一半</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>argue</v>
       </c>
       <c r="B35" t="str">
-        <v>faithful</v>
+        <v>/ˈɑːrɡjuː/</v>
       </c>
       <c r="C35" t="str">
-        <v>忠实的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>faithful(忠实的)📢</v>
+        <v>争论</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>neighbour</v>
       </c>
       <c r="B36" t="str">
-        <v>salad</v>
+        <v>/ˈneɪbər/</v>
       </c>
       <c r="C36" t="str">
-        <v>沙拉</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D36" t="str">
-        <v>salad(沙拉)📢</v>
+        <v>邻居</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>crust</v>
       </c>
       <c r="B37" t="str">
-        <v>couple</v>
+        <v>/krʌst/</v>
       </c>
       <c r="C37" t="str">
-        <v>一对</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>couple(一对)📢</v>
+        <v>外壳</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>district</v>
       </c>
       <c r="B38" t="str">
-        <v>strong</v>
+        <v>/ˈdɪstrɪkt/</v>
       </c>
       <c r="C38" t="str">
-        <v>强壮的</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>strong(强壮的)📢</v>
+        <v>区域</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>ox</v>
       </c>
       <c r="B39" t="str">
-        <v>front</v>
+        <v>/ɑːks/</v>
       </c>
       <c r="C39" t="str">
-        <v>前面</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>front(前面)📢</v>
+        <v>牛</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>sea</v>
       </c>
       <c r="B40" t="str">
-        <v>half</v>
+        <v>/siː/</v>
       </c>
       <c r="C40" t="str">
-        <v>一半</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>half(一半)📢</v>
+        <v>大海</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>guarantee</v>
       </c>
       <c r="B41" t="str">
-        <v>argue</v>
+        <v>/ˌɡærənˈtiː/</v>
       </c>
       <c r="C41" t="str">
-        <v>争论</v>
+        <v>n./vt.</v>
       </c>
       <c r="D41" t="str">
-        <v>argue(争论)📢</v>
+        <v>保证</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>thorn</v>
       </c>
       <c r="B42" t="str">
-        <v>neighbour</v>
+        <v>/θɔːrn/</v>
       </c>
       <c r="C42" t="str">
-        <v>邻居</v>
+        <v>n.</v>
       </c>
       <c r="D42" t="str">
-        <v>neighbour(邻居)📢</v>
+        <v>荆棘</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>appear</v>
       </c>
       <c r="B43" t="str">
-        <v>cold</v>
+        <v>/əˈpɪr/</v>
       </c>
       <c r="C43" t="str">
-        <v>寒冷的</v>
+        <v>vi./v.</v>
       </c>
       <c r="D43" t="str">
-        <v>cold(寒冷的)📢</v>
+        <v>出现</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>against</v>
       </c>
       <c r="B44" t="str">
-        <v>sheet</v>
+        <v>/əˈɡeɪnst/</v>
       </c>
       <c r="C44" t="str">
-        <v>薄片</v>
+        <v>prep.</v>
       </c>
       <c r="D44" t="str">
-        <v>sheet(薄片)📢</v>
+        <v>反对</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>dose</v>
       </c>
       <c r="B45" t="str">
-        <v>tree</v>
+        <v>/doʊs/</v>
       </c>
       <c r="C45" t="str">
-        <v>树</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>tree(树)📢</v>
+        <v>剂量</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>release</v>
       </c>
       <c r="B46" t="str">
-        <v>crust</v>
+        <v>/rɪˈliːs/</v>
       </c>
       <c r="C46" t="str">
-        <v>外壳</v>
+        <v>n./vt.</v>
       </c>
       <c r="D46" t="str">
-        <v>crust(外壳)📢</v>
+        <v>释放</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>acceptance</v>
       </c>
       <c r="B47" t="str">
-        <v>expensive</v>
+        <v>/əkˈseptəns/</v>
       </c>
       <c r="C47" t="str">
-        <v>昂贵的</v>
+        <v>n.</v>
       </c>
       <c r="D47" t="str">
-        <v>expensive(昂贵的)📢</v>
+        <v>接纳</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>gesture</v>
       </c>
       <c r="B48" t="str">
-        <v>district</v>
+        <v>/ˈdʒestʃər/</v>
       </c>
       <c r="C48" t="str">
-        <v>区域</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>district(区域)📢</v>
+        <v>手势</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>therefore</v>
       </c>
       <c r="B49" t="str">
-        <v>ox</v>
+        <v>/ˈðerfɔːr/</v>
       </c>
       <c r="C49" t="str">
-        <v>牛</v>
+        <v>v./adv.</v>
       </c>
       <c r="D49" t="str">
-        <v>ox(牛)📢</v>
+        <v>因此</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>instead</v>
       </c>
       <c r="B50" t="str">
-        <v>sea</v>
+        <v>/ɪnˈsted/</v>
       </c>
       <c r="C50" t="str">
-        <v>大海</v>
+        <v>v./adv.</v>
       </c>
       <c r="D50" t="str">
-        <v>sea(大海)📢</v>
+        <v>相反</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>me</v>
       </c>
       <c r="B51" t="str">
-        <v>educate</v>
+        <v>/mi; miː/</v>
       </c>
       <c r="C51" t="str">
-        <v>教育</v>
+        <v>n./pron.</v>
       </c>
       <c r="D51" t="str">
-        <v>educate(教育)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>quarterly</v>
-      </c>
-      <c r="C52" t="str">
-        <v>每季度</v>
-      </c>
-      <c r="D52" t="str">
-        <v>quarterly(每季度)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>poor</v>
-      </c>
-      <c r="C53" t="str">
-        <v>差</v>
-      </c>
-      <c r="D53" t="str">
-        <v>poor(差)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>guarantee</v>
-      </c>
-      <c r="C54" t="str">
-        <v>保证</v>
-      </c>
-      <c r="D54" t="str">
-        <v>guarantee(保证)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>faithful</v>
-      </c>
-      <c r="C55" t="str">
-        <v>忠实的</v>
-      </c>
-      <c r="D55" t="str">
-        <v>faithful(忠实的)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>thorn</v>
-      </c>
-      <c r="C56" t="str">
-        <v>荆棘</v>
-      </c>
-      <c r="D56" t="str">
-        <v>thorn(荆棘)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>appear</v>
-      </c>
-      <c r="C57" t="str">
-        <v>出现</v>
-      </c>
-      <c r="D57" t="str">
-        <v>appear(出现)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>against</v>
-      </c>
-      <c r="C58" t="str">
-        <v>反对</v>
-      </c>
-      <c r="D58" t="str">
-        <v>against(反对)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>dose</v>
-      </c>
-      <c r="C59" t="str">
-        <v>剂量</v>
-      </c>
-      <c r="D59" t="str">
-        <v>dose(剂量)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>release</v>
-      </c>
-      <c r="C60" t="str">
-        <v>释放</v>
-      </c>
-      <c r="D60" t="str">
-        <v>release(释放)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>British</v>
-      </c>
-      <c r="C61" t="str">
-        <v>英国的</v>
-      </c>
-      <c r="D61" t="str">
-        <v>British(英国的)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>acceptance</v>
-      </c>
-      <c r="C62" t="str">
-        <v>接纳</v>
-      </c>
-      <c r="D62" t="str">
-        <v>acceptance(接纳)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>gesture</v>
-      </c>
-      <c r="C63" t="str">
-        <v>手势</v>
-      </c>
-      <c r="D63" t="str">
-        <v>gesture(手势)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>gown</v>
-      </c>
-      <c r="C64" t="str">
-        <v>长袍</v>
-      </c>
-      <c r="D64" t="str">
-        <v>gown(长袍)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>tree</v>
-      </c>
-      <c r="C65" t="str">
-        <v>树</v>
-      </c>
-      <c r="D65" t="str">
-        <v>tree(树)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>poor</v>
-      </c>
-      <c r="C66" t="str">
-        <v>贫困的</v>
-      </c>
-      <c r="D66" t="str">
-        <v>poor(贫困的)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>monthly</v>
-      </c>
-      <c r="C67" t="str">
-        <v>每月的</v>
-      </c>
-      <c r="D67" t="str">
-        <v>monthly(每月的)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>sheet</v>
-      </c>
-      <c r="C68" t="str">
-        <v>表格</v>
-      </c>
-      <c r="D68" t="str">
-        <v>sheet(表格)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>store</v>
-      </c>
-      <c r="C69" t="str">
-        <v>商店</v>
-      </c>
-      <c r="D69" t="str">
-        <v>store(商店)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>afternoon</v>
-      </c>
-      <c r="C70" t="str">
-        <v>下午</v>
-      </c>
-      <c r="D70" t="str">
-        <v>afternoon(下午)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>chart</v>
-      </c>
-      <c r="C71" t="str">
-        <v>图表</v>
-      </c>
-      <c r="D71" t="str">
-        <v>chart(图表)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>quarterly</v>
-      </c>
-      <c r="C72" t="str">
-        <v>季刊</v>
-      </c>
-      <c r="D72" t="str">
-        <v>quarterly(季刊)📢</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
-        <v>guarantee</v>
-      </c>
-      <c r="C73" t="str">
-        <v>保证</v>
-      </c>
-      <c r="D73" t="str">
-        <v>guarantee(保证)📢</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
-        <v>tree</v>
-      </c>
-      <c r="C74" t="str">
-        <v>树</v>
-      </c>
-      <c r="D74" t="str">
-        <v>tree(树)📢</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="str">
-        <v>atom</v>
-      </c>
-      <c r="C75" t="str">
-        <v>原子</v>
-      </c>
-      <c r="D75" t="str">
-        <v>atom(原子)📢</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="str">
-        <v>argue</v>
-      </c>
-      <c r="C76" t="str">
-        <v>争论</v>
-      </c>
-      <c r="D76" t="str">
-        <v>argue(争论)📢</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="str">
-        <v>therefore</v>
-      </c>
-      <c r="C77" t="str">
-        <v>因此</v>
-      </c>
-      <c r="D77" t="str">
-        <v>therefore(因此)📢</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="str">
-        <v>juice</v>
-      </c>
-      <c r="C78" t="str">
-        <v>果汁</v>
-      </c>
-      <c r="D78" t="str">
-        <v>juice(果汁)📢</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="str">
-        <v>poor</v>
-      </c>
-      <c r="C79" t="str">
-        <v>贫困的</v>
-      </c>
-      <c r="D79" t="str">
-        <v>poor(贫困的)📢</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="str">
-        <v>instead</v>
-      </c>
-      <c r="C80" t="str">
-        <v>相反</v>
-      </c>
-      <c r="D80" t="str">
-        <v>instead(相反)📢</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81">
-        <v>80</v>
-      </c>
-      <c r="B81" t="str">
-        <v>educate</v>
-      </c>
-      <c r="C81" t="str">
-        <v>教育</v>
-      </c>
-      <c r="D81" t="str">
-        <v>educate(教育)📢</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82">
-        <v>81</v>
-      </c>
-      <c r="B82" t="str">
-        <v>therefore</v>
-      </c>
-      <c r="C82" t="str">
-        <v>因此</v>
-      </c>
-      <c r="D82" t="str">
-        <v>therefore(因此)📢</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83">
-        <v>82</v>
-      </c>
-      <c r="B83" t="str">
-        <v>tree</v>
-      </c>
-      <c r="C83" t="str">
-        <v>树</v>
-      </c>
-      <c r="D83" t="str">
-        <v>tree(树)📢</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84">
-        <v>83</v>
-      </c>
-      <c r="B84" t="str">
-        <v>atom</v>
-      </c>
-      <c r="C84" t="str">
-        <v>原子</v>
-      </c>
-      <c r="D84" t="str">
-        <v>atom(原子)📢</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85">
-        <v>84</v>
-      </c>
-      <c r="B85" t="str">
-        <v>mostly</v>
-      </c>
-      <c r="C85" t="str">
-        <v>主要</v>
-      </c>
-      <c r="D85" t="str">
-        <v>mostly(主要)📢</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86">
-        <v>85</v>
-      </c>
-      <c r="B86" t="str">
-        <v>me</v>
-      </c>
-      <c r="C86" t="str">
         <v>我</v>
-      </c>
-      <c r="D86" t="str">
-        <v>me(我)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D86"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>